--- a/college_data_template.xlsx
+++ b/college_data_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nanda Kishore\.gemini\antigravity\scratch\student_performance_monitoring\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B5592EB-9582-4252-84CB-3F8B33C8AB20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF59D596-317A-479A-8D7C-8C75E2676129}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="📋 Instructions" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1104" uniqueCount="412">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1104" uniqueCount="411">
   <si>
     <t xml:space="preserve">  🎓 College Data Import Template — Instructions</t>
   </si>
@@ -1254,9 +1254,6 @@
   </si>
   <si>
     <t>Absent</t>
-  </si>
-  <si>
-    <t>23r11a60202</t>
   </si>
   <si>
     <t>aravindailaveni@gmail.com</t>
@@ -1480,6 +1477,9 @@
   </cellStyles>
   <dxfs count="22">
     <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
       <alignment vertical="center" wrapText="1"/>
     </dxf>
     <dxf>
@@ -1575,9 +1575,6 @@
       </font>
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1595,9 +1592,9 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table8" displayName="Table8" ref="A1:C7" totalsRowShown="0">
   <autoFilter ref="A1:C7" xr:uid="{00000000-0009-0000-0100-000008000000}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="department_code" dataDxfId="20"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="department_name" dataDxfId="19"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="hod_username" dataDxfId="18"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="department_code" dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="department_name" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="hod_username" dataDxfId="19"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1625,19 +1622,19 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table3" displayName="Table3" ref="A1:M32" totalsRowShown="0">
   <autoFilter ref="A1:M32" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="username" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="password" dataDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="full_name" dataDxfId="15"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="email" dataDxfId="14"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="phone" dataDxfId="13"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="roll_number" dataDxfId="12"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="department_code" dataDxfId="11"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="year" dataDxfId="10"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="section" dataDxfId="9"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" name="attendance_pct" dataDxfId="8"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0200-00000B000000}" name="parent_name" dataDxfId="7"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0200-00000C000000}" name="parent_email" dataDxfId="6"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0200-00000D000000}" name="parent_phone" dataDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="username" dataDxfId="18"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="password" dataDxfId="17"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="full_name" dataDxfId="16"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="email" dataDxfId="15"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="phone" dataDxfId="14"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="roll_number" dataDxfId="13"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="department_code" dataDxfId="12"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="year" dataDxfId="11"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="section" dataDxfId="10"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" name="attendance_pct" dataDxfId="9"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0200-00000B000000}" name="parent_name" dataDxfId="8"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0200-00000C000000}" name="parent_email" dataDxfId="7"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0200-00000D000000}" name="parent_phone" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1647,11 +1644,11 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="Table2" displayName="Table2" ref="A1:E146" totalsRowShown="0">
   <autoFilter ref="A1:E146" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="roll_number" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="subject" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="internal_marks" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="assignment_scores" dataDxfId="1"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="exam_marks" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="roll_number" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="subject" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="internal_marks" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="assignment_scores" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="exam_marks" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1662,7 +1659,7 @@
   <autoFilter ref="A1:E100" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="roll_number"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="date" dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="date" dataDxfId="0"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="subject"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="status"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" name="Percentage"/>
@@ -3007,22 +3004,22 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="7" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="B6" s="7" t="s">
+        <v>410</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>406</v>
+      </c>
+      <c r="D6" s="14" t="s">
         <v>409</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>407</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>410</v>
       </c>
       <c r="E6" s="7">
         <v>9000000004</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="G6" s="7" t="s">
         <v>46</v>
@@ -3037,10 +3034,10 @@
         <v>20</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="L6" s="14" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="M6" s="7">
         <v>9100000004</v>
@@ -4506,7 +4503,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="6" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>370</v>
@@ -4523,7 +4520,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="6" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>371</v>
@@ -4540,7 +4537,7 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="6" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>373</v>
@@ -4557,7 +4554,7 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="6" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>372</v>
@@ -7015,7 +7012,7 @@
     </row>
     <row r="15" spans="1:9" ht="16.05" customHeight="1">
       <c r="A15" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B15" s="4">
         <v>46193</v>
@@ -7033,7 +7030,7 @@
     </row>
     <row r="16" spans="1:9" ht="16.05" customHeight="1">
       <c r="A16" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B16" s="4">
         <v>46194</v>
@@ -7051,7 +7048,7 @@
     </row>
     <row r="17" spans="1:9" ht="16.05" customHeight="1">
       <c r="A17" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B17" s="4">
         <v>46195</v>
@@ -7069,7 +7066,7 @@
     </row>
     <row r="18" spans="1:9" ht="16.05" customHeight="1">
       <c r="A18" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B18" s="4">
         <v>46196</v>

--- a/college_data_template.xlsx
+++ b/college_data_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nanda Kishore\.gemini\antigravity\scratch\student_performance_monitoring\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF59D596-317A-479A-8D7C-8C75E2676129}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7342A256-029D-4FDC-AD2A-8165E5FFF6D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="📋 Instructions" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1104" uniqueCount="411">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1104" uniqueCount="410">
   <si>
     <t xml:space="preserve">  🎓 College Data Import Template — Instructions</t>
   </si>
@@ -1121,9 +1121,6 @@
     <t>Mahesh Kumar Sr.</t>
   </si>
   <si>
-    <t>mahesh.parent@gcet.edu.in</t>
-  </si>
-  <si>
     <t>subject</t>
   </si>
   <si>
@@ -1265,13 +1262,13 @@
     <t>Komuraiah</t>
   </si>
   <si>
-    <t>23r11a60203</t>
-  </si>
-  <si>
     <t>23r11a0203@gcet.edu.in</t>
   </si>
   <si>
     <t>23r11a0203</t>
+  </si>
+  <si>
+    <t>maheshrajpanke@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -3004,16 +3001,16 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="7" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="E6" s="7">
         <v>9000000004</v>
@@ -3034,10 +3031,10 @@
         <v>20</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="L6" s="14" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="M6" s="7">
         <v>9100000004</v>
@@ -4225,8 +4222,8 @@
       <c r="K35" t="s">
         <v>359</v>
       </c>
-      <c r="L35" t="s">
-        <v>360</v>
+      <c r="L35" s="8" t="s">
+        <v>409</v>
       </c>
       <c r="M35">
         <v>7032797095</v>
@@ -4243,10 +4240,11 @@
     <hyperlink ref="L34" r:id="rId2" xr:uid="{00000000-0004-0000-0300-000001000000}"/>
     <hyperlink ref="D6" r:id="rId3" xr:uid="{DC278D84-0A0A-49D7-BE43-5E400D9D5A32}"/>
     <hyperlink ref="L6" r:id="rId4" xr:uid="{F85AD79B-1AE3-4987-8EE2-F2E14B421944}"/>
+    <hyperlink ref="L35" r:id="rId5" xr:uid="{0ECA2740-0CB9-468D-B689-2306222AB105}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart r:id="rId5"/>
+    <tablePart r:id="rId6"/>
   </tableParts>
 </worksheet>
 </file>
@@ -4268,33 +4266,33 @@
         <v>152</v>
       </c>
       <c r="B1" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>361</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="5" t="s">
         <v>362</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>363</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="18" customHeight="1">
       <c r="A2" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>368</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1">
@@ -4302,7 +4300,7 @@
         <v>172</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C3" s="7">
         <v>24</v>
@@ -4319,7 +4317,7 @@
         <v>172</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C4" s="7">
         <v>26</v>
@@ -4353,7 +4351,7 @@
         <v>172</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C6" s="7">
         <v>25</v>
@@ -4370,7 +4368,7 @@
         <v>179</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C7" s="7">
         <v>28</v>
@@ -4387,7 +4385,7 @@
         <v>179</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C8" s="7">
         <v>27</v>
@@ -4421,7 +4419,7 @@
         <v>179</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C10" s="7">
         <v>29</v>
@@ -4438,7 +4436,7 @@
         <v>185</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C11" s="7">
         <v>21</v>
@@ -4455,7 +4453,7 @@
         <v>185</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C12" s="7">
         <v>23</v>
@@ -4489,7 +4487,7 @@
         <v>185</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C14" s="7">
         <v>22</v>
@@ -4503,10 +4501,10 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="6" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C15" s="7">
         <v>19</v>
@@ -4520,10 +4518,10 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="6" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C16" s="7">
         <v>21</v>
@@ -4537,10 +4535,10 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="6" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C17" s="7">
         <v>18</v>
@@ -4554,10 +4552,10 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="6" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C18" s="7">
         <v>20</v>
@@ -4574,7 +4572,7 @@
         <v>191</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C19" s="7">
         <v>26</v>
@@ -4591,7 +4589,7 @@
         <v>191</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C20" s="7">
         <v>27</v>
@@ -4625,7 +4623,7 @@
         <v>191</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C22" s="7">
         <v>28</v>
@@ -4642,7 +4640,7 @@
         <v>197</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C23" s="7">
         <v>23</v>
@@ -4659,7 +4657,7 @@
         <v>197</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C24" s="7">
         <v>25</v>
@@ -4693,7 +4691,7 @@
         <v>197</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C26" s="7">
         <v>24</v>
@@ -4710,7 +4708,7 @@
         <v>203</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C27" s="7">
         <v>27</v>
@@ -4727,7 +4725,7 @@
         <v>203</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C28" s="7">
         <v>28</v>
@@ -4761,7 +4759,7 @@
         <v>203</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C30" s="7">
         <v>29</v>
@@ -4778,7 +4776,7 @@
         <v>209</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C31" s="7">
         <v>25</v>
@@ -4795,7 +4793,7 @@
         <v>209</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C32" s="7">
         <v>26</v>
@@ -4829,7 +4827,7 @@
         <v>209</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C34" s="7">
         <v>27</v>
@@ -4846,7 +4844,7 @@
         <v>215</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C35" s="7">
         <v>22</v>
@@ -4863,7 +4861,7 @@
         <v>215</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C36" s="7">
         <v>23</v>
@@ -4897,7 +4895,7 @@
         <v>215</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C38" s="7">
         <v>24</v>
@@ -4914,7 +4912,7 @@
         <v>221</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C39" s="7">
         <v>28</v>
@@ -4931,7 +4929,7 @@
         <v>221</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C40" s="7">
         <v>27</v>
@@ -4965,7 +4963,7 @@
         <v>221</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C42" s="7">
         <v>29</v>
@@ -4979,10 +4977,10 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="6" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C43" s="7">
         <v>22</v>
@@ -4996,10 +4994,10 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="6" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C44" s="7">
         <v>24</v>
@@ -5013,7 +5011,7 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="6" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B45" s="7" t="s">
         <v>44</v>
@@ -5030,10 +5028,10 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="6" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C46" s="7">
         <v>23</v>
@@ -5047,10 +5045,10 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="6" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C47" s="7">
         <v>25</v>
@@ -5064,10 +5062,10 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="6" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C48" s="7">
         <v>26</v>
@@ -5081,7 +5079,7 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="6" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B49" s="7" t="s">
         <v>53</v>
@@ -5098,10 +5096,10 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="6" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C50" s="7">
         <v>27</v>
@@ -5115,10 +5113,10 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="6" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C51" s="7">
         <v>28</v>
@@ -5132,10 +5130,10 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="6" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C52" s="7">
         <v>27</v>
@@ -5149,7 +5147,7 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="6" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B53" s="7" t="s">
         <v>55</v>
@@ -5166,10 +5164,10 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="6" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C54" s="7">
         <v>29</v>
@@ -5183,10 +5181,10 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="6" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C55" s="7">
         <v>20</v>
@@ -5200,10 +5198,10 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="6" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C56" s="7">
         <v>22</v>
@@ -5217,10 +5215,10 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="6" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C57" s="7">
         <v>19</v>
@@ -5234,10 +5232,10 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="6" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C58" s="7">
         <v>21</v>
@@ -5251,10 +5249,10 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="6" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C59" s="7">
         <v>26</v>
@@ -5268,10 +5266,10 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="6" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C60" s="7">
         <v>27</v>
@@ -5285,7 +5283,7 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="6" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B61" s="7" t="s">
         <v>44</v>
@@ -5302,10 +5300,10 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="6" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C62" s="7">
         <v>28</v>
@@ -5319,10 +5317,10 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="6" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C63" s="7">
         <v>23</v>
@@ -5336,10 +5334,10 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="6" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C64" s="7">
         <v>25</v>
@@ -5353,7 +5351,7 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="6" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B65" s="7" t="s">
         <v>53</v>
@@ -5370,10 +5368,10 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="6" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C66" s="7">
         <v>24</v>
@@ -5387,10 +5385,10 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="6" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C67" s="7">
         <v>27</v>
@@ -5404,10 +5402,10 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="6" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C68" s="7">
         <v>28</v>
@@ -5421,7 +5419,7 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="6" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B69" s="7" t="s">
         <v>55</v>
@@ -5438,10 +5436,10 @@
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="6" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C70" s="7">
         <v>29</v>
@@ -5455,10 +5453,10 @@
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="6" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C71" s="7">
         <v>19</v>
@@ -5472,10 +5470,10 @@
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="6" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C72" s="7">
         <v>21</v>
@@ -5489,10 +5487,10 @@
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="6" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B73" s="7" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C73" s="7">
         <v>18</v>
@@ -5506,10 +5504,10 @@
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="6" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C74" s="7">
         <v>20</v>
@@ -5523,10 +5521,10 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="6" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B75" s="7" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C75" s="7">
         <v>25</v>
@@ -5540,10 +5538,10 @@
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="6" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B76" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C76" s="7">
         <v>26</v>
@@ -5557,7 +5555,7 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="6" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B77" s="7" t="s">
         <v>44</v>
@@ -5574,10 +5572,10 @@
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="6" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B78" s="7" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C78" s="7">
         <v>27</v>
@@ -5591,10 +5589,10 @@
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="6" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C79" s="7">
         <v>22</v>
@@ -5608,10 +5606,10 @@
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="6" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B80" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C80" s="7">
         <v>23</v>
@@ -5625,7 +5623,7 @@
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="6" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B81" s="7" t="s">
         <v>53</v>
@@ -5642,10 +5640,10 @@
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="6" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C82" s="7">
         <v>24</v>
@@ -5659,10 +5657,10 @@
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="6" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C83" s="7">
         <v>27</v>
@@ -5676,10 +5674,10 @@
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="6" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C84" s="7">
         <v>28</v>
@@ -5693,7 +5691,7 @@
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="6" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B85" s="7" t="s">
         <v>55</v>
@@ -5710,10 +5708,10 @@
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="6" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B86" s="7" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C86" s="7">
         <v>29</v>
@@ -5727,10 +5725,10 @@
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="6" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B87" s="7" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C87" s="7">
         <v>20</v>
@@ -5744,10 +5742,10 @@
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="6" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C88" s="7">
         <v>22</v>
@@ -5761,10 +5759,10 @@
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="6" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B89" s="7" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C89" s="7">
         <v>19</v>
@@ -5778,10 +5776,10 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="6" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B90" s="7" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C90" s="7">
         <v>21</v>
@@ -5795,10 +5793,10 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="6" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B91" s="7" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C91" s="7">
         <v>25</v>
@@ -5812,10 +5810,10 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="6" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B92" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C92" s="7">
         <v>26</v>
@@ -5829,7 +5827,7 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="6" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B93" s="7" t="s">
         <v>44</v>
@@ -5846,10 +5844,10 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="6" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B94" s="7" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C94" s="7">
         <v>27</v>
@@ -5863,10 +5861,10 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B95" s="7" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C95" s="7">
         <v>22</v>
@@ -5880,10 +5878,10 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B96" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C96" s="7">
         <v>23</v>
@@ -5897,7 +5895,7 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B97" s="7" t="s">
         <v>53</v>
@@ -5914,10 +5912,10 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B98" s="7" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C98" s="7">
         <v>24</v>
@@ -5931,10 +5929,10 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="6" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B99" s="7" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C99" s="7">
         <v>28</v>
@@ -5948,10 +5946,10 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="6" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B100" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C100" s="7">
         <v>27</v>
@@ -5965,7 +5963,7 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="6" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>55</v>
@@ -5982,10 +5980,10 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="6" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B102" s="7" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C102" s="7">
         <v>29</v>
@@ -5999,10 +5997,10 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="6" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B103" s="7" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C103" s="7">
         <v>19</v>
@@ -6016,10 +6014,10 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="6" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B104" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C104" s="7">
         <v>21</v>
@@ -6033,10 +6031,10 @@
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="6" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B105" s="7" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C105" s="7">
         <v>18</v>
@@ -6050,10 +6048,10 @@
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="6" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B106" s="7" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C106" s="7">
         <v>20</v>
@@ -6067,10 +6065,10 @@
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="6" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B107" s="7" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C107" s="7">
         <v>25</v>
@@ -6084,10 +6082,10 @@
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="6" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B108" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C108" s="7">
         <v>26</v>
@@ -6101,7 +6099,7 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="6" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B109" s="7" t="s">
         <v>44</v>
@@ -6118,10 +6116,10 @@
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="6" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B110" s="7" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C110" s="7">
         <v>27</v>
@@ -6135,10 +6133,10 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="6" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B111" s="7" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C111" s="7">
         <v>23</v>
@@ -6152,10 +6150,10 @@
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="6" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B112" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C112" s="7">
         <v>25</v>
@@ -6169,7 +6167,7 @@
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="6" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B113" s="7" t="s">
         <v>53</v>
@@ -6186,10 +6184,10 @@
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="6" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B114" s="7" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C114" s="7">
         <v>24</v>
@@ -6203,10 +6201,10 @@
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="6" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B115" s="7" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C115" s="7">
         <v>27</v>
@@ -6220,10 +6218,10 @@
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="6" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B116" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C116" s="7">
         <v>28</v>
@@ -6237,7 +6235,7 @@
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="6" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B117" s="7" t="s">
         <v>55</v>
@@ -6254,10 +6252,10 @@
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="6" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B118" s="7" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C118" s="7">
         <v>29</v>
@@ -6271,10 +6269,10 @@
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="6" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B119" s="7" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C119" s="7">
         <v>20</v>
@@ -6288,10 +6286,10 @@
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="6" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B120" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C120" s="7">
         <v>22</v>
@@ -6305,10 +6303,10 @@
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="6" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B121" s="7" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C121" s="7">
         <v>19</v>
@@ -6322,10 +6320,10 @@
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="6" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B122" s="7" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C122" s="7">
         <v>21</v>
@@ -6339,10 +6337,10 @@
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="6" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B123" s="7" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C123" s="7">
         <v>25</v>
@@ -6356,10 +6354,10 @@
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="6" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B124" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C124" s="7">
         <v>26</v>
@@ -6373,7 +6371,7 @@
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="6" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B125" s="7" t="s">
         <v>44</v>
@@ -6390,10 +6388,10 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="6" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B126" s="7" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C126" s="7">
         <v>27</v>
@@ -6407,10 +6405,10 @@
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="6" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B127" s="7" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C127" s="7">
         <v>22</v>
@@ -6424,10 +6422,10 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="6" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B128" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C128" s="7">
         <v>23</v>
@@ -6441,7 +6439,7 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="6" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B129" s="7" t="s">
         <v>53</v>
@@ -6458,10 +6456,10 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="6" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B130" s="7" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C130" s="7">
         <v>24</v>
@@ -6475,10 +6473,10 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="6" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B131" s="7" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C131" s="7">
         <v>28</v>
@@ -6492,10 +6490,10 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="6" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B132" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C132" s="7">
         <v>27</v>
@@ -6509,7 +6507,7 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="6" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B133" s="7" t="s">
         <v>55</v>
@@ -6526,10 +6524,10 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="6" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B134" s="7" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C134" s="7">
         <v>29</v>
@@ -6546,7 +6544,7 @@
         <v>346</v>
       </c>
       <c r="B135" s="7" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C135" s="7">
         <v>22</v>
@@ -6563,7 +6561,7 @@
         <v>346</v>
       </c>
       <c r="B136" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C136" s="7">
         <v>21</v>
@@ -6597,7 +6595,7 @@
         <v>346</v>
       </c>
       <c r="B138" s="7" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C138" s="7">
         <v>20</v>
@@ -6614,7 +6612,7 @@
         <v>351</v>
       </c>
       <c r="B139" s="7" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C139" s="7">
         <v>25</v>
@@ -6631,7 +6629,7 @@
         <v>351</v>
       </c>
       <c r="B140" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C140" s="7">
         <v>24</v>
@@ -6665,7 +6663,7 @@
         <v>351</v>
       </c>
       <c r="B142" s="7" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C142" s="7">
         <v>23</v>
@@ -6682,7 +6680,7 @@
         <v>356</v>
       </c>
       <c r="B143" s="7" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C143" s="7">
         <v>27</v>
@@ -6699,7 +6697,7 @@
         <v>356</v>
       </c>
       <c r="B144" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C144" s="7">
         <v>26</v>
@@ -6733,7 +6731,7 @@
         <v>356</v>
       </c>
       <c r="B146" s="7" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C146" s="7">
         <v>25</v>
@@ -6773,30 +6771,30 @@
         <v>152</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>361</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>398</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="18" customHeight="1">
       <c r="A2" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>400</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>401</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="16.05" customHeight="1">
@@ -6807,10 +6805,10 @@
         <v>46193</v>
       </c>
       <c r="C3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D3" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E3">
         <v>85</v>
@@ -6824,10 +6822,10 @@
         <v>46194</v>
       </c>
       <c r="C4" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D4" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E4">
         <v>85</v>
@@ -6844,7 +6842,7 @@
         <v>44</v>
       </c>
       <c r="D5" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E5">
         <v>85</v>
@@ -6858,10 +6856,10 @@
         <v>46196</v>
       </c>
       <c r="C6" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D6" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E6">
         <v>85</v>
@@ -6875,10 +6873,10 @@
         <v>46193</v>
       </c>
       <c r="C7" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D7" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E7">
         <v>91</v>
@@ -6892,10 +6890,10 @@
         <v>46194</v>
       </c>
       <c r="C8" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D8" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E8">
         <v>91</v>
@@ -6913,7 +6911,7 @@
         <v>44</v>
       </c>
       <c r="D9" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E9">
         <v>91</v>
@@ -6928,10 +6926,10 @@
         <v>46196</v>
       </c>
       <c r="C10" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D10" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E10">
         <v>91</v>
@@ -6946,10 +6944,10 @@
         <v>46193</v>
       </c>
       <c r="C11" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D11" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E11">
         <v>72</v>
@@ -6964,10 +6962,10 @@
         <v>46194</v>
       </c>
       <c r="C12" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D12" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E12">
         <v>72</v>
@@ -6985,7 +6983,7 @@
         <v>44</v>
       </c>
       <c r="D13" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E13">
         <v>72</v>
@@ -7000,10 +6998,10 @@
         <v>46196</v>
       </c>
       <c r="C14" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D14" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E14">
         <v>72</v>
@@ -7012,16 +7010,16 @@
     </row>
     <row r="15" spans="1:9" ht="16.05" customHeight="1">
       <c r="A15" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B15" s="4">
         <v>46193</v>
       </c>
       <c r="C15" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D15" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E15">
         <v>67</v>
@@ -7030,16 +7028,16 @@
     </row>
     <row r="16" spans="1:9" ht="16.05" customHeight="1">
       <c r="A16" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B16" s="4">
         <v>46194</v>
       </c>
       <c r="C16" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D16" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E16">
         <v>67</v>
@@ -7048,16 +7046,16 @@
     </row>
     <row r="17" spans="1:9" ht="16.05" customHeight="1">
       <c r="A17" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B17" s="4">
         <v>46195</v>
       </c>
       <c r="C17" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D17" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E17">
         <v>67</v>
@@ -7066,16 +7064,16 @@
     </row>
     <row r="18" spans="1:9" ht="16.05" customHeight="1">
       <c r="A18" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B18" s="4">
         <v>46196</v>
       </c>
       <c r="C18" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D18" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E18">
         <v>30</v>
@@ -7090,10 +7088,10 @@
         <v>46193</v>
       </c>
       <c r="C19" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D19" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E19">
         <v>88</v>
@@ -7108,10 +7106,10 @@
         <v>46194</v>
       </c>
       <c r="C20" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D20" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E20">
         <v>88</v>
@@ -7129,7 +7127,7 @@
         <v>44</v>
       </c>
       <c r="D21" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E21">
         <v>88</v>
@@ -7144,10 +7142,10 @@
         <v>46196</v>
       </c>
       <c r="C22" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D22" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E22">
         <v>88</v>
@@ -7162,10 +7160,10 @@
         <v>46193</v>
       </c>
       <c r="C23" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D23" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E23">
         <v>85</v>
@@ -7180,10 +7178,10 @@
         <v>46194</v>
       </c>
       <c r="C24" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D24" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E24">
         <v>85</v>
@@ -7201,7 +7199,7 @@
         <v>53</v>
       </c>
       <c r="D25" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E25">
         <v>85</v>
@@ -7216,10 +7214,10 @@
         <v>46196</v>
       </c>
       <c r="C26" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D26" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E26">
         <v>85</v>
@@ -7234,10 +7232,10 @@
         <v>46193</v>
       </c>
       <c r="C27" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D27" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E27">
         <v>91</v>
@@ -7252,10 +7250,10 @@
         <v>46194</v>
       </c>
       <c r="C28" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D28" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E28">
         <v>91</v>
@@ -7273,7 +7271,7 @@
         <v>55</v>
       </c>
       <c r="D29" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E29">
         <v>91</v>
@@ -7288,10 +7286,10 @@
         <v>46196</v>
       </c>
       <c r="C30" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D30" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E30">
         <v>91</v>
@@ -7306,10 +7304,10 @@
         <v>46193</v>
       </c>
       <c r="C31" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D31" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E31">
         <v>90</v>
@@ -7324,10 +7322,10 @@
         <v>46194</v>
       </c>
       <c r="C32" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D32" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E32">
         <v>90</v>
@@ -7345,7 +7343,7 @@
         <v>44</v>
       </c>
       <c r="D33" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E33">
         <v>90</v>
@@ -7360,10 +7358,10 @@
         <v>46196</v>
       </c>
       <c r="C34" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D34" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E34">
         <v>90</v>
@@ -7378,10 +7376,10 @@
         <v>46193</v>
       </c>
       <c r="C35" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D35" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E35">
         <v>82</v>
@@ -7396,10 +7394,10 @@
         <v>46194</v>
       </c>
       <c r="C36" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D36" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E36">
         <v>82</v>
@@ -7417,7 +7415,7 @@
         <v>53</v>
       </c>
       <c r="D37" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E37">
         <v>82</v>
@@ -7432,10 +7430,10 @@
         <v>46196</v>
       </c>
       <c r="C38" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D38" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E38">
         <v>82</v>
@@ -7450,10 +7448,10 @@
         <v>46193</v>
       </c>
       <c r="C39" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D39" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E39">
         <v>91</v>
@@ -7468,10 +7466,10 @@
         <v>46194</v>
       </c>
       <c r="C40" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D40" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E40">
         <v>91</v>
@@ -7489,7 +7487,7 @@
         <v>55</v>
       </c>
       <c r="D41" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E41">
         <v>91</v>
@@ -7504,10 +7502,10 @@
         <v>46196</v>
       </c>
       <c r="C42" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D42" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E42">
         <v>91</v>
@@ -7516,16 +7514,16 @@
     </row>
     <row r="43" spans="1:9" ht="16.05" customHeight="1">
       <c r="A43" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B43" s="4">
         <v>46193</v>
       </c>
       <c r="C43" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D43" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E43">
         <v>87</v>
@@ -7534,16 +7532,16 @@
     </row>
     <row r="44" spans="1:9" ht="16.05" customHeight="1">
       <c r="A44" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B44" s="4">
         <v>46194</v>
       </c>
       <c r="C44" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D44" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E44">
         <v>87</v>
@@ -7552,7 +7550,7 @@
     </row>
     <row r="45" spans="1:9" ht="16.05" customHeight="1">
       <c r="A45" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B45" s="4">
         <v>46195</v>
@@ -7561,7 +7559,7 @@
         <v>44</v>
       </c>
       <c r="D45" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E45">
         <v>87</v>
@@ -7570,16 +7568,16 @@
     </row>
     <row r="46" spans="1:9" ht="16.05" customHeight="1">
       <c r="A46" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B46" s="4">
         <v>46196</v>
       </c>
       <c r="C46" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D46" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E46">
         <v>87</v>
@@ -7588,16 +7586,16 @@
     </row>
     <row r="47" spans="1:9" ht="16.05" customHeight="1">
       <c r="A47" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B47" s="4">
         <v>46193</v>
       </c>
       <c r="C47" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D47" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E47">
         <v>92</v>
@@ -7606,16 +7604,16 @@
     </row>
     <row r="48" spans="1:9" ht="16.05" customHeight="1">
       <c r="A48" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B48" s="4">
         <v>46194</v>
       </c>
       <c r="C48" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D48" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E48">
         <v>92</v>
@@ -7624,7 +7622,7 @@
     </row>
     <row r="49" spans="1:9" ht="16.05" customHeight="1">
       <c r="A49" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B49" s="4">
         <v>46195</v>
@@ -7633,7 +7631,7 @@
         <v>53</v>
       </c>
       <c r="D49" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E49">
         <v>92</v>
@@ -7642,16 +7640,16 @@
     </row>
     <row r="50" spans="1:9" ht="16.05" customHeight="1">
       <c r="A50" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B50" s="4">
         <v>46196</v>
       </c>
       <c r="C50" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D50" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E50">
         <v>92</v>
@@ -7660,16 +7658,16 @@
     </row>
     <row r="51" spans="1:9" ht="16.05" customHeight="1">
       <c r="A51" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B51" s="4">
         <v>46193</v>
       </c>
       <c r="C51" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D51" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E51">
         <v>89</v>
@@ -7678,16 +7676,16 @@
     </row>
     <row r="52" spans="1:9" ht="16.05" customHeight="1">
       <c r="A52" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B52" s="4">
         <v>46194</v>
       </c>
       <c r="C52" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D52" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E52">
         <v>89</v>
@@ -7696,7 +7694,7 @@
     </row>
     <row r="53" spans="1:9" ht="16.05" customHeight="1">
       <c r="A53" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B53" s="4">
         <v>46195</v>
@@ -7705,7 +7703,7 @@
         <v>55</v>
       </c>
       <c r="D53" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E53">
         <v>89</v>
@@ -7714,16 +7712,16 @@
     </row>
     <row r="54" spans="1:9" ht="16.05" customHeight="1">
       <c r="A54" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B54" s="4">
         <v>46196</v>
       </c>
       <c r="C54" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D54" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E54">
         <v>89</v>
@@ -7732,16 +7730,16 @@
     </row>
     <row r="55" spans="1:9" ht="16.05" customHeight="1">
       <c r="A55" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B55" s="4">
         <v>46193</v>
       </c>
       <c r="C55" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D55" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E55">
         <v>90</v>
@@ -7750,16 +7748,16 @@
     </row>
     <row r="56" spans="1:9" ht="16.05" customHeight="1">
       <c r="A56" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B56" s="4">
         <v>46194</v>
       </c>
       <c r="C56" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D56" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E56">
         <v>90</v>
@@ -7768,16 +7766,16 @@
     </row>
     <row r="57" spans="1:9" ht="16.05" customHeight="1">
       <c r="A57" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B57" s="4">
         <v>46195</v>
       </c>
       <c r="C57" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D57" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E57">
         <v>90</v>
@@ -7786,16 +7784,16 @@
     </row>
     <row r="58" spans="1:9" ht="16.05" customHeight="1">
       <c r="A58" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B58" s="4">
         <v>46196</v>
       </c>
       <c r="C58" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D58" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E58">
         <v>90</v>
@@ -7804,16 +7802,16 @@
     </row>
     <row r="59" spans="1:9" ht="16.05" customHeight="1">
       <c r="A59" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B59" s="4">
         <v>46193</v>
       </c>
       <c r="C59" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D59" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E59">
         <v>84</v>
@@ -7822,16 +7820,16 @@
     </row>
     <row r="60" spans="1:9" ht="16.05" customHeight="1">
       <c r="A60" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B60" s="4">
         <v>46194</v>
       </c>
       <c r="C60" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D60" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E60">
         <v>84</v>
@@ -7840,7 +7838,7 @@
     </row>
     <row r="61" spans="1:9" ht="16.05" customHeight="1">
       <c r="A61" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B61" s="4">
         <v>46195</v>
@@ -7849,7 +7847,7 @@
         <v>44</v>
       </c>
       <c r="D61" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E61">
         <v>84</v>
@@ -7858,16 +7856,16 @@
     </row>
     <row r="62" spans="1:9" ht="16.05" customHeight="1">
       <c r="A62" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B62" s="4">
         <v>46196</v>
       </c>
       <c r="C62" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D62" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E62">
         <v>84</v>
@@ -7876,16 +7874,16 @@
     </row>
     <row r="63" spans="1:9" ht="16.05" customHeight="1">
       <c r="A63" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B63" s="4">
         <v>46193</v>
       </c>
       <c r="C63" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D63" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E63">
         <v>93</v>
@@ -7894,16 +7892,16 @@
     </row>
     <row r="64" spans="1:9" ht="16.05" customHeight="1">
       <c r="A64" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B64" s="4">
         <v>46194</v>
       </c>
       <c r="C64" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D64" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E64">
         <v>93</v>
@@ -7912,7 +7910,7 @@
     </row>
     <row r="65" spans="1:9" ht="16.05" customHeight="1">
       <c r="A65" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B65" s="4">
         <v>46195</v>
@@ -7921,7 +7919,7 @@
         <v>53</v>
       </c>
       <c r="D65" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E65">
         <v>93</v>
@@ -7930,16 +7928,16 @@
     </row>
     <row r="66" spans="1:9" ht="16.05" customHeight="1">
       <c r="A66" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B66" s="4">
         <v>46196</v>
       </c>
       <c r="C66" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D66" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E66">
         <v>93</v>
@@ -7948,16 +7946,16 @@
     </row>
     <row r="67" spans="1:9" ht="16.05" customHeight="1">
       <c r="A67" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B67" s="4">
         <v>46193</v>
       </c>
       <c r="C67" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D67" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E67">
         <v>88</v>
@@ -7966,16 +7964,16 @@
     </row>
     <row r="68" spans="1:9" ht="16.05" customHeight="1">
       <c r="A68" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B68" s="4">
         <v>46194</v>
       </c>
       <c r="C68" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D68" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E68">
         <v>88</v>
@@ -7984,7 +7982,7 @@
     </row>
     <row r="69" spans="1:9" ht="16.05" customHeight="1">
       <c r="A69" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B69" s="4">
         <v>46195</v>
@@ -7993,7 +7991,7 @@
         <v>55</v>
       </c>
       <c r="D69" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E69">
         <v>88</v>
@@ -8002,16 +8000,16 @@
     </row>
     <row r="70" spans="1:9" ht="16.05" customHeight="1">
       <c r="A70" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B70" s="4">
         <v>46196</v>
       </c>
       <c r="C70" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D70" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E70">
         <v>88</v>
@@ -8020,16 +8018,16 @@
     </row>
     <row r="71" spans="1:9" ht="16.05" customHeight="1">
       <c r="A71" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B71" s="4">
         <v>46193</v>
       </c>
       <c r="C71" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D71" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E71">
         <v>86</v>
@@ -8038,16 +8036,16 @@
     </row>
     <row r="72" spans="1:9" ht="16.05" customHeight="1">
       <c r="A72" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B72" s="4">
         <v>46194</v>
       </c>
       <c r="C72" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D72" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E72">
         <v>86</v>
@@ -8056,16 +8054,16 @@
     </row>
     <row r="73" spans="1:9" ht="16.05" customHeight="1">
       <c r="A73" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B73" s="4">
         <v>46195</v>
       </c>
       <c r="C73" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D73" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E73">
         <v>86</v>
@@ -8074,16 +8072,16 @@
     </row>
     <row r="74" spans="1:9" ht="16.05" customHeight="1">
       <c r="A74" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B74" s="4">
         <v>46196</v>
       </c>
       <c r="C74" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D74" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E74">
         <v>86</v>
@@ -8092,16 +8090,16 @@
     </row>
     <row r="75" spans="1:9" ht="16.05" customHeight="1">
       <c r="A75" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B75" s="4">
         <v>46193</v>
       </c>
       <c r="C75" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D75" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E75">
         <v>91</v>
@@ -8110,16 +8108,16 @@
     </row>
     <row r="76" spans="1:9" ht="16.05" customHeight="1">
       <c r="A76" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B76" s="4">
         <v>46194</v>
       </c>
       <c r="C76" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D76" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E76">
         <v>91</v>
@@ -8128,7 +8126,7 @@
     </row>
     <row r="77" spans="1:9" ht="16.05" customHeight="1">
       <c r="A77" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B77" s="4">
         <v>46195</v>
@@ -8137,7 +8135,7 @@
         <v>44</v>
       </c>
       <c r="D77" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E77">
         <v>91</v>
@@ -8146,16 +8144,16 @@
     </row>
     <row r="78" spans="1:9" ht="16.05" customHeight="1">
       <c r="A78" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B78" s="4">
         <v>46196</v>
       </c>
       <c r="C78" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D78" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E78">
         <v>91</v>
@@ -8164,16 +8162,16 @@
     </row>
     <row r="79" spans="1:9" ht="16.05" customHeight="1">
       <c r="A79" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B79" s="4">
         <v>46193</v>
       </c>
       <c r="C79" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D79" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E79">
         <v>87</v>
@@ -8182,16 +8180,16 @@
     </row>
     <row r="80" spans="1:9" ht="16.05" customHeight="1">
       <c r="A80" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B80" s="4">
         <v>46194</v>
       </c>
       <c r="C80" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D80" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E80">
         <v>87</v>
@@ -8200,7 +8198,7 @@
     </row>
     <row r="81" spans="1:9" ht="16.05" customHeight="1">
       <c r="A81" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B81" s="4">
         <v>46195</v>
@@ -8209,7 +8207,7 @@
         <v>53</v>
       </c>
       <c r="D81" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E81">
         <v>87</v>
@@ -8218,16 +8216,16 @@
     </row>
     <row r="82" spans="1:9">
       <c r="A82" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B82" s="4">
         <v>46196</v>
       </c>
       <c r="C82" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D82" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E82">
         <v>87</v>
@@ -8236,16 +8234,16 @@
     </row>
     <row r="83" spans="1:9">
       <c r="A83" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B83" s="4">
         <v>46193</v>
       </c>
       <c r="C83" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D83" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E83">
         <v>92</v>
@@ -8254,16 +8252,16 @@
     </row>
     <row r="84" spans="1:9">
       <c r="A84" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B84" s="4">
         <v>46194</v>
       </c>
       <c r="C84" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D84" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E84">
         <v>92</v>
@@ -8272,7 +8270,7 @@
     </row>
     <row r="85" spans="1:9">
       <c r="A85" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B85" s="4">
         <v>46195</v>
@@ -8281,7 +8279,7 @@
         <v>55</v>
       </c>
       <c r="D85" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E85">
         <v>92</v>
@@ -8290,16 +8288,16 @@
     </row>
     <row r="86" spans="1:9">
       <c r="A86" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B86" s="4">
         <v>46196</v>
       </c>
       <c r="C86" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D86" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E86">
         <v>92</v>
@@ -8308,16 +8306,16 @@
     </row>
     <row r="87" spans="1:9">
       <c r="A87" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B87" s="4">
         <v>46193</v>
       </c>
       <c r="C87" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D87" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E87">
         <v>85</v>
@@ -8326,16 +8324,16 @@
     </row>
     <row r="88" spans="1:9">
       <c r="A88" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B88" s="4">
         <v>46194</v>
       </c>
       <c r="C88" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D88" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E88">
         <v>86</v>
@@ -8350,10 +8348,10 @@
         <v>46193</v>
       </c>
       <c r="C89" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D89" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E89">
         <v>85</v>
@@ -8368,10 +8366,10 @@
         <v>46194</v>
       </c>
       <c r="C90" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D90" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E90">
         <v>85</v>
@@ -8389,7 +8387,7 @@
         <v>53</v>
       </c>
       <c r="D91" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E91">
         <v>85</v>
@@ -8404,10 +8402,10 @@
         <v>46196</v>
       </c>
       <c r="C92" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D92" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E92">
         <v>85</v>
@@ -8422,10 +8420,10 @@
         <v>46193</v>
       </c>
       <c r="C93" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D93" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E93">
         <v>58</v>
@@ -8440,10 +8438,10 @@
         <v>46194</v>
       </c>
       <c r="C94" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D94" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E94">
         <v>68</v>
@@ -8461,7 +8459,7 @@
         <v>53</v>
       </c>
       <c r="D95" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E95">
         <v>18</v>
@@ -8476,10 +8474,10 @@
         <v>46196</v>
       </c>
       <c r="C96" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D96" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E96">
         <v>88</v>
@@ -8494,10 +8492,10 @@
         <v>46193</v>
       </c>
       <c r="C97" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D97" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E97">
         <v>65</v>
@@ -8512,10 +8510,10 @@
         <v>46194</v>
       </c>
       <c r="C98" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D98" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E98">
         <v>65</v>
@@ -8533,7 +8531,7 @@
         <v>53</v>
       </c>
       <c r="D99" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E99">
         <v>69</v>
@@ -8548,10 +8546,10 @@
         <v>46196</v>
       </c>
       <c r="C100" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D100" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E100">
         <v>65</v>
